--- a/forms/trg/Formulir_TRG_ppm.xlsx
+++ b/forms/trg/Formulir_TRG_ppm.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
